--- a/data/trans_orig/P15A-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P15A-Estudios-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha tenido un accidente en los últimos tres meses que le ha causado heridas o lesiones suficientes para limitar su actividad normal y/o para necesitar asistencia sanitaria en 2007</t>
+          <t>Población que ha tenido un accidente en los últimos tres meses que le ha causado heridas o lesiones suficientes para limitar su actividad normal y/o para necesitar asistencia sanitaria en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>17176</t>
+          <t>16638</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>37117</t>
+          <t>36396</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,53%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>33328</t>
+          <t>34224</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>59703</t>
+          <t>60424</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>4,54%</t>
+          <t>4,59%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>55385</t>
+          <t>55786</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>89332</t>
+          <t>89490</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,7 +818,7 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,38%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>994606</t>
+          <t>995327</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1014547</t>
+          <t>1015085</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>96,4%</t>
+          <t>96,47%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,34%</t>
+          <t>98,39%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1255410</t>
+          <t>1254689</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1281785</t>
+          <t>1280889</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>95,46%</t>
+          <t>95,41%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>97,47%</t>
+          <t>97,4%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>2257503</t>
+          <t>2257345</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>2291450</t>
+          <t>2291049</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -936,7 +936,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,64%</t>
+          <t>97,62%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>60459</t>
+          <t>63335</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>95378</t>
+          <t>98133</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>3,74%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,63%</t>
+          <t>5,79%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>24505</t>
+          <t>24017</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>48052</t>
+          <t>46732</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>2,94%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>93964</t>
+          <t>93622</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>137299</t>
+          <t>138015</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,18%</t>
+          <t>4,21%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1598035</t>
+          <t>1595280</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1632954</t>
+          <t>1630078</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>94,37%</t>
+          <t>94,21%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>96,43%</t>
+          <t>96,26%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1539621</t>
+          <t>1540941</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1563168</t>
+          <t>1563656</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>96,97%</t>
+          <t>97,06%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,46%</t>
+          <t>98,49%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3143787</t>
+          <t>3143071</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3187122</t>
+          <t>3187464</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>95,82%</t>
+          <t>95,79%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,14%</t>
+          <t>97,15%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>11551</t>
+          <t>11469</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>30549</t>
+          <t>31383</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,54%</t>
+          <t>5,69%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>6366</t>
+          <t>7061</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>22156</t>
+          <t>21631</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,65%</t>
+          <t>4,54%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>22442</t>
+          <t>21862</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>47136</t>
+          <t>46379</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,59%</t>
+          <t>4,51%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>520859</t>
+          <t>520025</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>539857</t>
+          <t>539939</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>94,46%</t>
+          <t>94,31%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,91%</t>
+          <t>97,92%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>454256</t>
+          <t>454781</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>470046</t>
+          <t>469351</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>95,35%</t>
+          <t>95,46%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,66%</t>
+          <t>98,52%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>980684</t>
+          <t>981441</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1005378</t>
+          <t>1005958</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>95,41%</t>
+          <t>95,49%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,82%</t>
+          <t>97,87%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>102111</t>
+          <t>103130</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>144855</t>
+          <t>147090</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>3,15%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>4,49%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>75288</t>
+          <t>75267</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>115059</t>
+          <t>116065</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1817,7 +1817,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,43%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>189848</t>
+          <t>190759</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>251213</t>
+          <t>249424</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,77%</t>
+          <t>3,75%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3131688</t>
+          <t>3129453</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3174432</t>
+          <t>3173413</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>95,58%</t>
+          <t>95,51%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>96,88%</t>
+          <t>96,85%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3264138</t>
+          <t>3263132</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3303909</t>
+          <t>3303930</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,7 +1925,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>96,6%</t>
+          <t>96,57%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6404528</t>
+          <t>6406317</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6465893</t>
+          <t>6464982</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,23%</t>
+          <t>96,25%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,15%</t>
+          <t>97,13%</t>
         </is>
       </c>
     </row>
@@ -2141,7 +2141,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha tenido un accidente en los últimos tres meses que le ha causado heridas o lesiones suficientes para limitar su actividad normal y/o para necesitar asistencia sanitaria en 2012</t>
+          <t>Población que ha tenido un accidente en los últimos tres meses que le ha causado heridas o lesiones suficientes para limitar su actividad normal y/o para necesitar asistencia sanitaria en 2012 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2336,12 +2336,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>15411</t>
+          <t>15819</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>38484</t>
+          <t>37566</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2351,12 +2351,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>3,85%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2371,12 +2371,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>32345</t>
+          <t>32008</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>58419</t>
+          <t>58691</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2386,12 +2386,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>4,37%</t>
+          <t>4,39%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2406,12 +2406,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>51931</t>
+          <t>50380</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>83826</t>
+          <t>85549</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2421,12 +2421,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>3,7%</t>
         </is>
       </c>
     </row>
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>936159</t>
+          <t>937077</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>959232</t>
+          <t>958824</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2464,12 +2464,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>96,05%</t>
+          <t>96,15%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,42%</t>
+          <t>98,38%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2484,12 +2484,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1279378</t>
+          <t>1279106</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1305452</t>
+          <t>1305789</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2499,12 +2499,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>95,63%</t>
+          <t>95,61%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>97,58%</t>
+          <t>97,61%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2519,12 +2519,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>2228614</t>
+          <t>2226891</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>2260509</t>
+          <t>2262060</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2534,12 +2534,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>96,37%</t>
+          <t>96,3%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,75%</t>
+          <t>97,82%</t>
         </is>
       </c>
     </row>
@@ -2679,12 +2679,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>47665</t>
+          <t>46542</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>80009</t>
+          <t>78526</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -2694,12 +2694,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -2714,12 +2714,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>28213</t>
+          <t>28997</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>53726</t>
+          <t>54495</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -2729,12 +2729,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>81652</t>
+          <t>83189</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>121390</t>
+          <t>124057</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2764,12 +2764,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>3,33%</t>
         </is>
       </c>
     </row>
@@ -2792,12 +2792,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1883948</t>
+          <t>1885431</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1916292</t>
+          <t>1917415</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2807,12 +2807,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>95,93%</t>
+          <t>96,0%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,57%</t>
+          <t>97,63%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1704077</t>
+          <t>1703308</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1729590</t>
+          <t>1728806</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -2842,12 +2842,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>96,94%</t>
+          <t>96,9%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,4%</t>
+          <t>98,35%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3600370</t>
+          <t>3597703</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3640108</t>
+          <t>3638571</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2877,12 +2877,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,74%</t>
+          <t>96,67%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,81%</t>
+          <t>97,76%</t>
         </is>
       </c>
     </row>
@@ -3022,12 +3022,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>6945</t>
+          <t>7281</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>23203</t>
+          <t>23570</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3037,12 +3037,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,82%</t>
+          <t>4,9%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3057,12 +3057,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>8436</t>
+          <t>8035</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>27535</t>
+          <t>25974</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3072,12 +3072,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>6,0%</t>
+          <t>5,66%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>18548</t>
+          <t>18950</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>42206</t>
+          <t>42676</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3107,12 +3107,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>4,54%</t>
         </is>
       </c>
     </row>
@@ -3135,12 +3135,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>457978</t>
+          <t>457611</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>474236</t>
+          <t>473900</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>95,18%</t>
+          <t>95,1%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,56%</t>
+          <t>98,49%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3170,12 +3170,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>431096</t>
+          <t>432657</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>450195</t>
+          <t>450596</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>94,0%</t>
+          <t>94,34%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,16%</t>
+          <t>98,25%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3205,12 +3205,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>897607</t>
+          <t>897137</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>921265</t>
+          <t>920863</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3220,12 +3220,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>95,51%</t>
+          <t>95,46%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,03%</t>
+          <t>97,98%</t>
         </is>
       </c>
     </row>
@@ -3365,12 +3365,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>79204</t>
+          <t>79933</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>122541</t>
+          <t>119072</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3380,12 +3380,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>3,48%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3400,12 +3400,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>79374</t>
+          <t>78075</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>118674</t>
+          <t>120934</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3435,12 +3435,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>169874</t>
+          <t>171054</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>226958</t>
+          <t>229339</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3450,12 +3450,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>3,29%</t>
         </is>
       </c>
     </row>
@@ -3478,12 +3478,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3297241</t>
+          <t>3300710</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3340578</t>
+          <t>3339849</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3493,12 +3493,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,42%</t>
+          <t>96,52%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,68%</t>
+          <t>97,66%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3513,12 +3513,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3435556</t>
+          <t>3433296</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3474856</t>
+          <t>3476155</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3528,12 +3528,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>96,66%</t>
+          <t>96,6%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,77%</t>
+          <t>97,8%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3548,12 +3548,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6747054</t>
+          <t>6744673</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6804138</t>
+          <t>6802958</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3563,12 +3563,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,75%</t>
+          <t>96,71%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,56%</t>
+          <t>97,55%</t>
         </is>
       </c>
     </row>
@@ -3744,7 +3744,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha tenido un accidente en los últimos tres meses que le ha causado heridas o lesiones suficientes para limitar su actividad normal y/o para necesitar asistencia sanitaria en 2016</t>
+          <t>Población que ha tenido un accidente en los últimos tres meses que le ha causado heridas o lesiones suficientes para limitar su actividad normal y/o para necesitar asistencia sanitaria en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3939,12 +3939,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>13577</t>
+          <t>13625</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>30349</t>
+          <t>30586</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3954,12 +3954,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>4,05%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3974,12 +3974,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>30438</t>
+          <t>30168</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>58032</t>
+          <t>57557</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3989,12 +3989,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>3,03%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,83%</t>
+          <t>5,79%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4009,12 +4009,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>47617</t>
+          <t>48016</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>80892</t>
+          <t>79822</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4024,12 +4024,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,75%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>4,56%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>723998</t>
+          <t>723761</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>740770</t>
+          <t>740722</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>95,98%</t>
+          <t>95,95%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,2%</t>
+          <t>98,19%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>936628</t>
+          <t>937103</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>964222</t>
+          <t>964492</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>94,17%</t>
+          <t>94,21%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>96,94%</t>
+          <t>96,97%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1668115</t>
+          <t>1669185</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1701390</t>
+          <t>1700991</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>95,38%</t>
+          <t>95,44%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,28%</t>
+          <t>97,25%</t>
         </is>
       </c>
     </row>
@@ -4282,12 +4282,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>40429</t>
+          <t>40813</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>70401</t>
+          <t>70120</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4297,12 +4297,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>3,38%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4317,12 +4317,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>20764</t>
+          <t>21637</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>44262</t>
+          <t>46009</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4332,12 +4332,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>67662</t>
+          <t>68915</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>106594</t>
+          <t>106754</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4367,12 +4367,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,63%</t>
         </is>
       </c>
     </row>
@@ -4395,12 +4395,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2005984</t>
+          <t>2006265</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2035956</t>
+          <t>2035572</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4410,12 +4410,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>96,61%</t>
+          <t>96,62%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,05%</t>
+          <t>98,03%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4430,12 +4430,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1944038</t>
+          <t>1942291</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1967536</t>
+          <t>1966663</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4445,12 +4445,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>97,77%</t>
+          <t>97,69%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,96%</t>
+          <t>98,91%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4465,12 +4465,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3958091</t>
+          <t>3957931</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3997023</t>
+          <t>3995770</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4480,12 +4480,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,38%</t>
+          <t>97,37%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,34%</t>
+          <t>98,3%</t>
         </is>
       </c>
     </row>
@@ -4625,12 +4625,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>6057</t>
+          <t>5820</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>21388</t>
+          <t>21075</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4640,12 +4640,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>3,85%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4660,12 +4660,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>7329</t>
+          <t>7566</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>22278</t>
+          <t>23267</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4675,12 +4675,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,06%</t>
+          <t>4,24%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4695,12 +4695,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>17178</t>
+          <t>16374</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>38647</t>
+          <t>37320</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4710,12 +4710,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>3,41%</t>
         </is>
       </c>
     </row>
@@ -4738,12 +4738,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>525498</t>
+          <t>525811</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>540829</t>
+          <t>541066</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>96,09%</t>
+          <t>96,15%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,89%</t>
+          <t>98,94%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4773,12 +4773,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>526862</t>
+          <t>525873</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>541811</t>
+          <t>541574</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4788,12 +4788,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>95,94%</t>
+          <t>95,76%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,67%</t>
+          <t>98,62%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4808,12 +4808,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1057380</t>
+          <t>1058707</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1078849</t>
+          <t>1079653</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4823,12 +4823,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>96,47%</t>
+          <t>96,59%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,43%</t>
+          <t>98,51%</t>
         </is>
       </c>
     </row>
@@ -4968,12 +4968,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>70392</t>
+          <t>69741</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>107003</t>
+          <t>106532</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4983,12 +4983,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>3,15%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5003,12 +5003,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>68628</t>
+          <t>70194</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>110214</t>
+          <t>110290</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5018,7 +5018,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -5038,12 +5038,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>149330</t>
+          <t>150882</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>206168</t>
+          <t>203058</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5053,12 +5053,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>2,94%</t>
         </is>
       </c>
     </row>
@@ -5081,12 +5081,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3270615</t>
+          <t>3271086</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3307226</t>
+          <t>3307877</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5096,12 +5096,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,83%</t>
+          <t>96,85%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,92%</t>
+          <t>97,94%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3421886</t>
+          <t>3421810</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3463472</t>
+          <t>3461906</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5136,7 +5136,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,06%</t>
+          <t>98,01%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5151,12 +5151,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6703550</t>
+          <t>6706660</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6760388</t>
+          <t>6758836</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5166,12 +5166,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,02%</t>
+          <t>97,06%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,84%</t>
+          <t>97,82%</t>
         </is>
       </c>
     </row>
@@ -5347,7 +5347,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha tenido un accidente en los últimos tres meses que le ha causado heridas o lesiones suficientes para limitar su actividad normal y/o para necesitar asistencia sanitaria en 2023</t>
+          <t>Población que ha tenido un accidente en los últimos tres meses que le ha causado heridas o lesiones suficientes para limitar su actividad normal y/o para necesitar asistencia sanitaria en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -5542,12 +5542,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>8457</t>
+          <t>8214</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>19436</t>
+          <t>19687</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5557,12 +5557,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,77%</t>
+          <t>3,82%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5577,12 +5577,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>31234</t>
+          <t>31515</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>49502</t>
+          <t>48274</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5592,12 +5592,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>4,13%</t>
+          <t>4,17%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>6,55%</t>
+          <t>6,39%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5612,12 +5612,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>42094</t>
+          <t>42447</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>63302</t>
+          <t>62784</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5627,12 +5627,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>3,34%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,98%</t>
+          <t>4,94%</t>
         </is>
       </c>
     </row>
@@ -5655,12 +5655,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>495502</t>
+          <t>495251</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>506481</t>
+          <t>506724</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5670,12 +5670,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>96,23%</t>
+          <t>96,18%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,36%</t>
+          <t>98,4%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5690,12 +5690,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>706006</t>
+          <t>707234</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>724274</t>
+          <t>723993</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5705,12 +5705,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>93,45%</t>
+          <t>93,61%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>95,87%</t>
+          <t>95,83%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5725,12 +5725,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1207144</t>
+          <t>1207662</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1228352</t>
+          <t>1227999</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5740,12 +5740,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>95,02%</t>
+          <t>95,06%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>96,69%</t>
+          <t>96,66%</t>
         </is>
       </c>
     </row>
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>31006</t>
+          <t>29981</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>68982</t>
+          <t>67462</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -5900,12 +5900,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5920,12 +5920,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>27608</t>
+          <t>27675</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>56364</t>
+          <t>56148</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5935,12 +5935,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,51%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5955,12 +5955,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>67233</t>
+          <t>68478</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>114396</t>
+          <t>114393</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5970,7 +5970,7 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
@@ -5998,12 +5998,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2221345</t>
+          <t>2222865</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2259321</t>
+          <t>2260346</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6013,12 +6013,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>96,99%</t>
+          <t>97,05%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,65%</t>
+          <t>98,69%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>2181459</t>
+          <t>2181675</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>2210215</t>
+          <t>2210148</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6048,12 +6048,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>97,48%</t>
+          <t>97,49%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,77%</t>
+          <t>98,76%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6068,12 +6068,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>4413754</t>
+          <t>4413757</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>4460917</t>
+          <t>4459672</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6088,7 +6088,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,52%</t>
+          <t>98,49%</t>
         </is>
       </c>
     </row>
@@ -6228,12 +6228,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>4808</t>
+          <t>4859</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>21982</t>
+          <t>22555</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6243,12 +6243,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,49%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6263,12 +6263,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>6434</t>
+          <t>6716</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>16801</t>
+          <t>16972</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6278,12 +6278,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6298,12 +6298,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>13922</t>
+          <t>13769</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>33299</t>
+          <t>33301</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6313,7 +6313,7 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
@@ -6341,12 +6341,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>624641</t>
+          <t>624068</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>641815</t>
+          <t>641764</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6356,12 +6356,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>96,6%</t>
+          <t>96,51%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,26%</t>
+          <t>99,25%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6376,12 +6376,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>643662</t>
+          <t>643491</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>654029</t>
+          <t>653747</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6391,12 +6391,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>97,46%</t>
+          <t>97,43%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,03%</t>
+          <t>98,98%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6411,12 +6411,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1273787</t>
+          <t>1273785</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1293164</t>
+          <t>1293317</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6431,7 +6431,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,93%</t>
+          <t>98,95%</t>
         </is>
       </c>
     </row>
@@ -6571,12 +6571,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>52434</t>
+          <t>53315</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>91869</t>
+          <t>94183</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6586,12 +6586,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6606,12 +6606,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>72830</t>
+          <t>71932</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>112957</t>
+          <t>110327</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6621,12 +6621,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6641,12 +6641,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>136761</t>
+          <t>135995</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>192298</t>
+          <t>190764</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6656,12 +6656,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,68%</t>
         </is>
       </c>
     </row>
@@ -6684,12 +6684,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3360020</t>
+          <t>3357706</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3399455</t>
+          <t>3398574</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6699,12 +6699,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>97,34%</t>
+          <t>97,27%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,48%</t>
+          <t>98,46%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6719,12 +6719,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3540837</t>
+          <t>3543467</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3580964</t>
+          <t>3581862</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6734,12 +6734,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>96,91%</t>
+          <t>96,98%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,01%</t>
+          <t>98,03%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6754,12 +6754,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6913385</t>
+          <t>6914919</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6968922</t>
+          <t>6969688</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6769,12 +6769,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,29%</t>
+          <t>97,32%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,08%</t>
+          <t>98,09%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P15A-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P15A-Estudios-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>16638</t>
+          <t>16444</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>36396</t>
+          <t>36145</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>34224</t>
+          <t>33402</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>60424</t>
+          <t>61304</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>4,59%</t>
+          <t>4,66%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>55786</t>
+          <t>56016</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>89490</t>
+          <t>89615</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>3,82%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>995327</t>
+          <t>995578</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1015085</t>
+          <t>1015279</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>96,47%</t>
+          <t>96,5%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,39%</t>
+          <t>98,41%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1254689</t>
+          <t>1253809</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1280889</t>
+          <t>1281711</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>95,41%</t>
+          <t>95,34%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>97,4%</t>
+          <t>97,46%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>2257345</t>
+          <t>2257220</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>2291049</t>
+          <t>2290819</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>96,19%</t>
+          <t>96,18%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,62%</t>
+          <t>97,61%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>63335</t>
+          <t>62559</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>98133</t>
+          <t>97144</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>3,69%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,79%</t>
+          <t>5,74%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>24017</t>
+          <t>24946</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>46732</t>
+          <t>49420</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>3,11%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>93622</t>
+          <t>94995</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>138015</t>
+          <t>135456</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,21%</t>
+          <t>4,13%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1595280</t>
+          <t>1596269</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1630078</t>
+          <t>1630854</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>94,21%</t>
+          <t>94,26%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>96,26%</t>
+          <t>96,31%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1540941</t>
+          <t>1538253</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1563656</t>
+          <t>1562727</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>97,06%</t>
+          <t>96,89%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,49%</t>
+          <t>98,43%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3143071</t>
+          <t>3145630</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3187464</t>
+          <t>3186091</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>95,79%</t>
+          <t>95,87%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,15%</t>
+          <t>97,1%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>11469</t>
+          <t>11131</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>31383</t>
+          <t>29909</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,69%</t>
+          <t>5,42%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>7061</t>
+          <t>6775</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>21631</t>
+          <t>22706</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,54%</t>
+          <t>4,77%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>21862</t>
+          <t>22886</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>46379</t>
+          <t>47152</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,51%</t>
+          <t>4,59%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>520025</t>
+          <t>521499</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>539939</t>
+          <t>540277</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>94,31%</t>
+          <t>94,58%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,92%</t>
+          <t>97,98%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>454781</t>
+          <t>453706</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>469351</t>
+          <t>469637</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>95,46%</t>
+          <t>95,23%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,52%</t>
+          <t>98,58%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>981441</t>
+          <t>980668</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1005958</t>
+          <t>1004934</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>95,49%</t>
+          <t>95,41%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,87%</t>
+          <t>97,77%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>103130</t>
+          <t>102848</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>147090</t>
+          <t>146963</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,7 +1777,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>3,14%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>75267</t>
+          <t>75895</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>116065</t>
+          <t>113942</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>3,37%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>190759</t>
+          <t>190398</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>249424</t>
+          <t>247827</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>2,86%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>3,72%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3129453</t>
+          <t>3129580</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3173413</t>
+          <t>3173695</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1895,7 +1895,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>96,85%</t>
+          <t>96,86%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3263132</t>
+          <t>3265255</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3303930</t>
+          <t>3303302</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>96,57%</t>
+          <t>96,63%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,77%</t>
+          <t>97,75%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6406317</t>
+          <t>6407914</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6464982</t>
+          <t>6465343</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,25%</t>
+          <t>96,28%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,13%</t>
+          <t>97,14%</t>
         </is>
       </c>
     </row>
@@ -2336,12 +2336,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>15819</t>
+          <t>15139</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>37566</t>
+          <t>36818</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2351,12 +2351,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,85%</t>
+          <t>3,78%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2371,12 +2371,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>32008</t>
+          <t>32585</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>58691</t>
+          <t>56950</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2386,12 +2386,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>4,26%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2406,12 +2406,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>50380</t>
+          <t>52294</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>85549</t>
+          <t>84897</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2421,12 +2421,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>3,67%</t>
         </is>
       </c>
     </row>
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>937077</t>
+          <t>937825</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>958824</t>
+          <t>959504</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2464,12 +2464,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>96,15%</t>
+          <t>96,22%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,38%</t>
+          <t>98,45%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2484,12 +2484,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1279106</t>
+          <t>1280847</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1305789</t>
+          <t>1305212</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2499,12 +2499,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>95,61%</t>
+          <t>95,74%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>97,61%</t>
+          <t>97,56%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2519,12 +2519,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>2226891</t>
+          <t>2227543</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>2262060</t>
+          <t>2260146</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2534,12 +2534,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>96,3%</t>
+          <t>96,33%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,82%</t>
+          <t>97,74%</t>
         </is>
       </c>
     </row>
@@ -2679,12 +2679,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>46542</t>
+          <t>47469</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>78526</t>
+          <t>78998</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -2694,12 +2694,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>4,02%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -2714,12 +2714,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>28997</t>
+          <t>28315</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>54495</t>
+          <t>53756</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -2729,12 +2729,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>3,06%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>83189</t>
+          <t>83380</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>124057</t>
+          <t>125283</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2769,7 +2769,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,37%</t>
         </is>
       </c>
     </row>
@@ -2792,12 +2792,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1885431</t>
+          <t>1884959</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1917415</t>
+          <t>1916488</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2807,12 +2807,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>96,0%</t>
+          <t>95,98%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,63%</t>
+          <t>97,58%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1703308</t>
+          <t>1704047</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1728806</t>
+          <t>1729488</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -2842,12 +2842,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>96,9%</t>
+          <t>96,94%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,35%</t>
+          <t>98,39%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3597703</t>
+          <t>3596477</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3638571</t>
+          <t>3638380</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2877,7 +2877,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,67%</t>
+          <t>96,63%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -3022,12 +3022,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>7281</t>
+          <t>6776</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>23570</t>
+          <t>23563</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3037,7 +3037,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -3057,12 +3057,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>8035</t>
+          <t>7488</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>25974</t>
+          <t>25577</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3072,12 +3072,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,66%</t>
+          <t>5,58%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>18950</t>
+          <t>18446</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>42676</t>
+          <t>41932</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3107,12 +3107,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,54%</t>
+          <t>4,46%</t>
         </is>
       </c>
     </row>
@@ -3135,12 +3135,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>457611</t>
+          <t>457618</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>473900</t>
+          <t>474405</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3155,7 +3155,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,49%</t>
+          <t>98,59%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3170,12 +3170,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>432657</t>
+          <t>433054</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>450596</t>
+          <t>451143</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>94,34%</t>
+          <t>94,42%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,25%</t>
+          <t>98,37%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3205,12 +3205,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>897137</t>
+          <t>897881</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>920863</t>
+          <t>921367</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3220,12 +3220,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>95,46%</t>
+          <t>95,54%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,98%</t>
+          <t>98,04%</t>
         </is>
       </c>
     </row>
@@ -3365,12 +3365,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>79933</t>
+          <t>79532</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>119072</t>
+          <t>119027</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3380,7 +3380,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -3400,12 +3400,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>78075</t>
+          <t>78935</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>120934</t>
+          <t>122308</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,44%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3435,12 +3435,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>171054</t>
+          <t>171094</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>229339</t>
+          <t>227506</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3455,7 +3455,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,26%</t>
         </is>
       </c>
     </row>
@@ -3478,12 +3478,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3300710</t>
+          <t>3300755</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3339849</t>
+          <t>3340250</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3498,7 +3498,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,66%</t>
+          <t>97,67%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3513,12 +3513,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3433296</t>
+          <t>3431922</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3476155</t>
+          <t>3475295</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3528,12 +3528,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>96,6%</t>
+          <t>96,56%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,8%</t>
+          <t>97,78%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3548,12 +3548,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6744673</t>
+          <t>6746506</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6802958</t>
+          <t>6802918</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3563,7 +3563,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,71%</t>
+          <t>96,74%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -3939,12 +3939,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>13625</t>
+          <t>14058</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>30586</t>
+          <t>31165</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3954,12 +3954,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,05%</t>
+          <t>4,13%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3974,12 +3974,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>30168</t>
+          <t>31058</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>57557</t>
+          <t>58265</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3989,12 +3989,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>3,12%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,79%</t>
+          <t>5,86%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4009,12 +4009,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>48016</t>
+          <t>49552</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>79822</t>
+          <t>80817</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4024,12 +4024,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>2,83%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>4,62%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>723761</t>
+          <t>723182</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>740722</t>
+          <t>740289</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>95,95%</t>
+          <t>95,87%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,19%</t>
+          <t>98,14%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>937103</t>
+          <t>936395</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>964492</t>
+          <t>963602</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>94,21%</t>
+          <t>94,14%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>96,97%</t>
+          <t>96,88%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1669185</t>
+          <t>1668190</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1700991</t>
+          <t>1699455</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>95,44%</t>
+          <t>95,38%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,25%</t>
+          <t>97,17%</t>
         </is>
       </c>
     </row>
@@ -4282,12 +4282,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>40813</t>
+          <t>39970</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>70120</t>
+          <t>69416</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4297,12 +4297,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>3,34%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4317,12 +4317,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>21637</t>
+          <t>21369</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>46009</t>
+          <t>45627</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4332,12 +4332,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>68915</t>
+          <t>67788</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>106754</t>
+          <t>104757</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4367,12 +4367,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,58%</t>
         </is>
       </c>
     </row>
@@ -4395,12 +4395,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2006265</t>
+          <t>2006969</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2035572</t>
+          <t>2036415</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4410,12 +4410,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>96,62%</t>
+          <t>96,66%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,03%</t>
+          <t>98,08%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4430,12 +4430,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1942291</t>
+          <t>1942673</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1966663</t>
+          <t>1966931</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4445,12 +4445,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>97,69%</t>
+          <t>97,71%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,91%</t>
+          <t>98,93%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4465,12 +4465,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3957931</t>
+          <t>3959928</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3995770</t>
+          <t>3996897</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4480,12 +4480,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,37%</t>
+          <t>97,42%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,3%</t>
+          <t>98,33%</t>
         </is>
       </c>
     </row>
@@ -4625,12 +4625,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>5820</t>
+          <t>6729</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>21075</t>
+          <t>20991</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4640,12 +4640,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,85%</t>
+          <t>3,84%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4660,12 +4660,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>7566</t>
+          <t>7809</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>23267</t>
+          <t>21684</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4675,12 +4675,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>3,95%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4695,12 +4695,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>16374</t>
+          <t>16550</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>37320</t>
+          <t>37725</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4710,12 +4710,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>3,44%</t>
         </is>
       </c>
     </row>
@@ -4738,12 +4738,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>525811</t>
+          <t>525895</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>541066</t>
+          <t>540157</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>96,15%</t>
+          <t>96,16%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,94%</t>
+          <t>98,77%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4773,12 +4773,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>525873</t>
+          <t>527456</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>541574</t>
+          <t>541331</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4788,12 +4788,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>95,76%</t>
+          <t>96,05%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,62%</t>
+          <t>98,58%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4808,12 +4808,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1058707</t>
+          <t>1058302</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1079653</t>
+          <t>1079477</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4823,12 +4823,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>96,59%</t>
+          <t>96,56%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,51%</t>
+          <t>98,49%</t>
         </is>
       </c>
     </row>
@@ -4968,12 +4968,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>69741</t>
+          <t>70714</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>106532</t>
+          <t>106822</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4983,12 +4983,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>2,09%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5003,12 +5003,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>70194</t>
+          <t>68820</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>110290</t>
+          <t>107479</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5018,12 +5018,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>3,04%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5038,12 +5038,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>150882</t>
+          <t>150717</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>203058</t>
+          <t>204200</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5058,7 +5058,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>2,96%</t>
         </is>
       </c>
     </row>
@@ -5081,12 +5081,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3271086</t>
+          <t>3270796</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3307877</t>
+          <t>3306904</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5096,12 +5096,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,85%</t>
+          <t>96,84%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,94%</t>
+          <t>97,91%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3421810</t>
+          <t>3424621</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3461906</t>
+          <t>3463280</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5131,12 +5131,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>96,88%</t>
+          <t>96,96%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,01%</t>
+          <t>98,05%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5151,12 +5151,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6706660</t>
+          <t>6705518</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6758836</t>
+          <t>6759001</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5166,7 +5166,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,06%</t>
+          <t>97,04%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -5537,32 +5537,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>12856</t>
+          <t>13531</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>8214</t>
+          <t>8298</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>19687</t>
+          <t>20935</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>3,62%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5572,32 +5572,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>39049</t>
+          <t>40749</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>31515</t>
+          <t>32571</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>48274</t>
+          <t>51397</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>5,17%</t>
+          <t>4,96%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>3,96%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>6,39%</t>
+          <t>6,25%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5607,32 +5607,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>51905</t>
+          <t>54280</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>42447</t>
+          <t>44094</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>62784</t>
+          <t>65590</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>3,88%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,15%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,94%</t>
+          <t>4,68%</t>
         </is>
       </c>
     </row>
@@ -5650,32 +5650,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>502082</t>
+          <t>564998</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>495251</t>
+          <t>557594</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>506724</t>
+          <t>570231</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>97,5%</t>
+          <t>97,66%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>96,18%</t>
+          <t>96,38%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,4%</t>
+          <t>98,57%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5685,32 +5685,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>716459</t>
+          <t>781289</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>707234</t>
+          <t>770641</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>723993</t>
+          <t>789467</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>94,83%</t>
+          <t>95,04%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>93,61%</t>
+          <t>93,75%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>95,83%</t>
+          <t>96,04%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5720,32 +5720,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>1218541</t>
+          <t>1346287</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1207662</t>
+          <t>1334977</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1227999</t>
+          <t>1356473</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>95,91%</t>
+          <t>96,12%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>95,06%</t>
+          <t>95,32%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>96,66%</t>
+          <t>96,85%</t>
         </is>
       </c>
     </row>
@@ -5763,17 +5763,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>514938</t>
+          <t>578529</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>514938</t>
+          <t>578529</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>514938</t>
+          <t>578529</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5798,17 +5798,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>755508</t>
+          <t>822038</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>755508</t>
+          <t>822038</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>755508</t>
+          <t>822038</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5833,17 +5833,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>1270446</t>
+          <t>1400567</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1270446</t>
+          <t>1400567</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>1270446</t>
+          <t>1400567</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5880,32 +5880,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>48276</t>
+          <t>55442</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>29981</t>
+          <t>40612</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>67462</t>
+          <t>77390</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>3,47%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5915,32 +5915,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>40950</t>
+          <t>44438</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>27675</t>
+          <t>33476</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>56148</t>
+          <t>60633</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5950,32 +5950,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>89226</t>
+          <t>99880</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>68478</t>
+          <t>78857</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>114393</t>
+          <t>124376</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,83%</t>
         </is>
       </c>
     </row>
@@ -5993,32 +5993,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>2242051</t>
+          <t>2175124</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2222865</t>
+          <t>2153176</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2260346</t>
+          <t>2189954</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>97,89%</t>
+          <t>97,51%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,05%</t>
+          <t>96,53%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,69%</t>
+          <t>98,18%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6028,32 +6028,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>2196873</t>
+          <t>2126954</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>2181675</t>
+          <t>2110759</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>2210148</t>
+          <t>2137916</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>98,17%</t>
+          <t>97,95%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>97,49%</t>
+          <t>97,21%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,76%</t>
+          <t>98,46%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6063,32 +6063,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>4438924</t>
+          <t>4302079</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>4413757</t>
+          <t>4277583</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>4459672</t>
+          <t>4323102</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>98,03%</t>
+          <t>97,73%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,47%</t>
+          <t>97,17%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,49%</t>
+          <t>98,21%</t>
         </is>
       </c>
     </row>
@@ -6106,17 +6106,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2290327</t>
+          <t>2230566</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2290327</t>
+          <t>2230566</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2290327</t>
+          <t>2230566</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -6141,17 +6141,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2237823</t>
+          <t>2171392</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2237823</t>
+          <t>2171392</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2237823</t>
+          <t>2171392</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -6176,17 +6176,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>4528150</t>
+          <t>4401959</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>4528150</t>
+          <t>4401959</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>4528150</t>
+          <t>4401959</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -6223,32 +6223,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>10613</t>
+          <t>12077</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>4859</t>
+          <t>5808</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>22555</t>
+          <t>22145</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>3,11%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6258,32 +6258,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>10898</t>
+          <t>13582</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>6716</t>
+          <t>8336</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>16972</t>
+          <t>20554</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6293,32 +6293,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>21511</t>
+          <t>25659</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>13769</t>
+          <t>17001</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>33301</t>
+          <t>38041</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,63%</t>
         </is>
       </c>
     </row>
@@ -6336,32 +6336,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>636010</t>
+          <t>699510</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>624068</t>
+          <t>689442</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>641764</t>
+          <t>705779</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>98,36%</t>
+          <t>98,3%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>96,51%</t>
+          <t>96,89%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,25%</t>
+          <t>99,18%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6371,32 +6371,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>649565</t>
+          <t>721295</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>643491</t>
+          <t>714323</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>653747</t>
+          <t>726541</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>98,35%</t>
+          <t>98,15%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>97,43%</t>
+          <t>97,2%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,98%</t>
+          <t>98,87%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6406,32 +6406,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>1285575</t>
+          <t>1420805</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1273785</t>
+          <t>1408423</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1293317</t>
+          <t>1429463</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>98,35%</t>
+          <t>98,23%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,45%</t>
+          <t>97,37%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,95%</t>
+          <t>98,82%</t>
         </is>
       </c>
     </row>
@@ -6449,17 +6449,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>646623</t>
+          <t>711587</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>646623</t>
+          <t>711587</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>646623</t>
+          <t>711587</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6484,17 +6484,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>660463</t>
+          <t>734877</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>660463</t>
+          <t>734877</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>660463</t>
+          <t>734877</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6519,17 +6519,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1307086</t>
+          <t>1446464</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1307086</t>
+          <t>1446464</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1307086</t>
+          <t>1446464</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6566,32 +6566,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>71746</t>
+          <t>81049</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>53315</t>
+          <t>62766</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>94183</t>
+          <t>104852</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>2,98%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6601,32 +6601,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>90896</t>
+          <t>98770</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>71932</t>
+          <t>81048</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>110327</t>
+          <t>118244</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,65%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6636,32 +6636,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>162642</t>
+          <t>179819</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>135995</t>
+          <t>154016</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>190764</t>
+          <t>206914</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,85%</t>
         </is>
       </c>
     </row>
@@ -6679,32 +6679,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>3380143</t>
+          <t>3439634</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3357706</t>
+          <t>3415831</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3398574</t>
+          <t>3457917</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>97,92%</t>
+          <t>97,7%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>97,27%</t>
+          <t>97,02%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,46%</t>
+          <t>98,22%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6714,32 +6714,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>3562898</t>
+          <t>3629537</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3543467</t>
+          <t>3610063</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3581862</t>
+          <t>3647259</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>97,51%</t>
+          <t>97,35%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>96,98%</t>
+          <t>96,83%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,03%</t>
+          <t>97,83%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6749,32 +6749,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>6943041</t>
+          <t>7069171</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6914919</t>
+          <t>7042076</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6969688</t>
+          <t>7094974</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>97,71%</t>
+          <t>97,52%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,32%</t>
+          <t>97,15%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,09%</t>
+          <t>97,88%</t>
         </is>
       </c>
     </row>
@@ -6792,17 +6792,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>3451889</t>
+          <t>3520683</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>3451889</t>
+          <t>3520683</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>3451889</t>
+          <t>3520683</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -6827,17 +6827,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>3653794</t>
+          <t>3728307</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>3653794</t>
+          <t>3728307</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>3653794</t>
+          <t>3728307</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -6862,17 +6862,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>7105683</t>
+          <t>7248990</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>7105683</t>
+          <t>7248990</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>7105683</t>
+          <t>7248990</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
